--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T13:20:09+00:00</t>
+    <t>2025-12-02T13:32:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T13:32:51+00:00</t>
+    <t>2025-12-02T13:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T13:33:21+00:00</t>
+    <t>2025-12-02T14:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T14:04:07+00:00</t>
+    <t>2025-12-02T14:19:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T14:19:50+00:00</t>
+    <t>2025-12-03T08:35:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T08:35:21+00:00</t>
+    <t>2026-01-06T09:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:36:59+00:00</t>
+    <t>2026-05-27T15:38:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:38:19+00:00</t>
+    <t>2026-05-27T15:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:45:18+00:00</t>
+    <t>2026-05-27T15:46:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:46:35+00:00</t>
+    <t>2026-05-27T15:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:54:25+00:00</t>
+    <t>2026-05-27T15:54:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:54:55+00:00</t>
+    <t>2026-05-27T15:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T15:59:28+00:00</t>
+    <t>2026-05-27T16:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T16:11:26+00:00</t>
+    <t>2026-05-27T16:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T16:13:17+00:00</t>
+    <t>2026-05-28T07:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T07:53:58+00:00</t>
+    <t>2026-05-28T08:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T08:04:13+00:00</t>
+    <t>2026-05-28T08:17:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ANS (https://esante.gouv.fr)</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T08:17:26+00:00</t>
+    <t>2026-05-28T08:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T08:25:32+00:00</t>
+    <t>2026-05-28T12:20:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T12:20:17+00:00</t>
+    <t>2026-05-28T12:25:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T12:25:51+00:00</t>
+    <t>2026-05-28T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T12:29:55+00:00</t>
+    <t>2026-05-28T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T13:37:46+00:00</t>
+    <t>2026-05-28T13:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T13:48:22+00:00</t>
+    <t>2026-05-28T13:58:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T13:58:36+00:00</t>
+    <t>2026-05-28T14:14:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:14:36+00:00</t>
+    <t>2026-06-01T11:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/nr-test-template-2/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:57:18+00:00</t>
+    <t>2026-06-01T14:14:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
